--- a/data/trans_orig/dukeGLOBAL-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/dukeGLOBAL-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala global de apoyo funcional social (Duke)</t>
+          <t>Puntuación media de la escala global de apoyo funcional social (Duke) (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,65; 47,76</t>
+          <t>46,65; 47,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,8; 49,84</t>
+          <t>48,81; 49,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,08; 47,25</t>
+          <t>46,04; 47,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,56; 48,94</t>
+          <t>47,55; 48,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,66; 46,04</t>
+          <t>44,66; 46,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,68; 48,8</t>
+          <t>47,71; 48,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,36; 46,51</t>
+          <t>45,31; 46,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,25; 48,27</t>
+          <t>47,3; 48,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,83; 46,75</t>
+          <t>45,87; 46,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,39; 49,18</t>
+          <t>48,34; 49,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,91; 46,74</t>
+          <t>45,85; 46,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,59; 48,4</t>
+          <t>47,6; 48,41</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,14; 48,18</t>
+          <t>47,15; 48,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,83; 48,79</t>
+          <t>47,81; 48,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,97; 47,82</t>
+          <t>46,95; 47,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,02; 52,1</t>
+          <t>48,02; 52,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,28; 47,38</t>
+          <t>46,24; 47,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 48,21</t>
+          <t>47,27; 48,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 47,47</t>
+          <t>46,64; 47,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,91; 47,82</t>
+          <t>46,83; 47,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,87; 47,59</t>
+          <t>46,85; 47,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,67; 48,34</t>
+          <t>47,73; 48,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,89; 47,53</t>
+          <t>46,89; 47,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,66; 50,71</t>
+          <t>47,64; 50,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,72; 48,99</t>
+          <t>47,66; 48,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,76; 48,92</t>
+          <t>47,79; 48,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,36; 46,31</t>
+          <t>45,33; 46,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,84; 48,99</t>
+          <t>47,79; 49,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,64; 47,93</t>
+          <t>46,69; 48,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,04; 48,12</t>
+          <t>47,01; 48,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,03; 46,01</t>
+          <t>44,99; 46,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,65; 49,27</t>
+          <t>47,64; 49,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,33; 48,28</t>
+          <t>47,42; 48,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,58; 48,41</t>
+          <t>47,61; 48,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,36; 46,04</t>
+          <t>45,34; 46,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,93; 48,88</t>
+          <t>47,9; 48,92</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,77; 47,8</t>
+          <t>46,76; 47,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,38; 48,28</t>
+          <t>47,32; 48,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,84; 47,77</t>
+          <t>46,83; 47,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,7; 48,82</t>
+          <t>47,74; 48,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,97; 47,03</t>
+          <t>45,9; 47,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,53; 47,46</t>
+          <t>46,52; 47,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,46; 47,42</t>
+          <t>46,37; 47,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,93; 49,94</t>
+          <t>47,89; 49,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 47,23</t>
+          <t>46,48; 47,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,05; 47,72</t>
+          <t>47,04; 47,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,78; 47,46</t>
+          <t>46,77; 47,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,22</t>
+          <t>47,96; 49,07</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,87</t>
+          <t>47,33; 47,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,13; 48,63</t>
+          <t>48,11; 48,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,64; 47,13</t>
+          <t>46,65; 47,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,17; 50,27</t>
+          <t>48,18; 50,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,21; 46,8</t>
+          <t>46,24; 46,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,36; 47,86</t>
+          <t>47,33; 47,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,24; 46,73</t>
+          <t>46,18; 46,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,69; 48,47</t>
+          <t>47,73; 48,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46,84; 47,26</t>
+          <t>46,86; 47,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,83; 48,18</t>
+          <t>47,8; 48,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,49; 46,84</t>
+          <t>46,5; 46,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,33</t>
+          <t>48,03; 49,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeGLOBAL-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/dukeGLOBAL-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48,23</t>
+          <t>47,93</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,79</t>
+          <t>47,69</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,0</t>
+          <t>47,81</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,65; 47,8</t>
+          <t>46,65; 47,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,81; 49,8</t>
+          <t>48,74; 49,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,04; 47,24</t>
+          <t>46,08; 47,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,55; 48,91</t>
+          <t>47,25; 48,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,66; 46,05</t>
+          <t>44,7; 46,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,71; 48,8</t>
+          <t>47,71; 48,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,31; 46,55</t>
+          <t>45,38; 46,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,3; 48,28</t>
+          <t>47,17; 48,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,87; 46,74</t>
+          <t>45,87; 46,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,34; 49,14</t>
+          <t>48,41; 49,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,85; 46,71</t>
+          <t>45,88; 46,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,6; 48,41</t>
+          <t>47,36; 48,25</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,6</t>
+          <t>48,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,37</t>
+          <t>47,17</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,61</t>
+          <t>47,58</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,15; 48,2</t>
+          <t>47,07; 48,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,81; 48,79</t>
+          <t>47,81; 48,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,95; 47,84</t>
+          <t>46,94; 47,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,02; 52,48</t>
+          <t>47,49; 48,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,24; 47,29</t>
+          <t>46,22; 47,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,27; 48,22</t>
+          <t>47,25; 48,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,64; 47,46</t>
+          <t>46,68; 47,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,83; 47,79</t>
+          <t>46,7; 47,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,85; 47,62</t>
+          <t>46,87; 47,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,73; 48,36</t>
+          <t>47,71; 48,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,89; 47,51</t>
+          <t>46,91; 47,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,64; 50,91</t>
+          <t>47,22; 47,91</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,4</t>
+          <t>48,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48,28</t>
+          <t>47,9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,34</t>
+          <t>47,96</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,66; 48,95</t>
+          <t>47,66; 48,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,79; 48,94</t>
+          <t>47,81; 49,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,33; 46,29</t>
+          <t>45,39; 46,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,79; 49,02</t>
+          <t>47,38; 48,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,69; 48,0</t>
+          <t>46,64; 47,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,01; 48,18</t>
+          <t>47,0; 48,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,99; 46,01</t>
+          <t>45,05; 46,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,64; 49,21</t>
+          <t>47,35; 48,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,42; 48,31</t>
+          <t>47,35; 48,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,61; 48,43</t>
+          <t>47,58; 48,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45,34; 46,01</t>
+          <t>45,35; 46,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,9; 48,92</t>
+          <t>47,55; 48,37</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48,29</t>
+          <t>48,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>48,51</t>
+          <t>47,82</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,41</t>
+          <t>47,93</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,76; 47,79</t>
+          <t>46,77; 47,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,32; 48,27</t>
+          <t>47,32; 48,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,74; 48,86</t>
+          <t>47,53; 48,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,9; 47,03</t>
+          <t>45,9; 47,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,37; 47,37</t>
+          <t>46,41; 47,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,89; 49,87</t>
+          <t>47,35; 48,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 47,24</t>
+          <t>46,46; 47,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,04; 47,72</t>
+          <t>47,09; 47,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,77; 47,43</t>
+          <t>46,78; 47,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,96; 49,07</t>
+          <t>47,56; 48,25</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,76</t>
+          <t>48,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>47,63</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>47,06</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>48,0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>47,06</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>48,0</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>46,68</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,38</t>
+          <t>47,81</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,89</t>
+          <t>47,31; 47,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>48,11; 48,64</t>
+          <t>48,17; 48,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,65; 47,12</t>
+          <t>46,66; 47,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,18; 50,32</t>
+          <t>47,71; 48,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,24; 46,82</t>
+          <t>46,23; 46,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,84</t>
+          <t>47,35; 47,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,18; 46,69</t>
+          <t>46,24; 46,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,73; 48,56</t>
+          <t>47,35; 47,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46,86; 47,25</t>
+          <t>46,84; 47,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,8; 48,16</t>
+          <t>47,81; 48,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,5; 46,85</t>
+          <t>46,51; 46,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,31</t>
+          <t>47,61; 47,99</t>
         </is>
       </c>
     </row>
